--- a/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,27 +518,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.37471669</t>
+          <t>-8.39377383</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.5512795</t>
+          <t>-74.57807864</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CLINICA ODONTOLOGICA GUERREROS</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO UNIVERSITARIO MAYUSHIN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SALVADOR ALLENDE 1065 1 POR EL COLEGIO NUEVO PARAISO CALLERIA CORONEL PORTILLO UCAYALI</t>
+          <t>CARRETERA FEDERICO BASADRE KM 6 200 INTERIOR UNIVERSIDAD NACIONAL DE UCAYALI DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.376165</t>
+          <t>-8.3833115</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.5266631</t>
+          <t>-74.5324882</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO DE LA MUJER</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "NUEVO AMANECER"</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MANCO CAPAC NUMERO 118 PISO 1 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>AVENIDA SAN FERNANDO MANZANA 14 LOTE 7 DISTRITO MANANTAY PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.3783522</t>
+          <t>-8.39101862</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.5450619</t>
+          <t>-74.54506736</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ESPECIALIZADO GABRIEL S.R.L</t>
+          <t>CENTRO MEDICO MUNICIPAL DE ATENCION BASICA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TRUJILLO NUMERO 726 MANZANA 265 LOTE 17-A DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS AAHH 9 OCTUBRE LT 2 MZ 24 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250101</t>
+          <t>250105</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -699,27 +699,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CALLERIA</t>
+          <t>YARINACOCHA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.37865862</t>
+          <t>-8.3646395</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.52837849</t>
+          <t>-74.5665971</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CLINICA AMAZONICA E.I.R.L</t>
+          <t>POLICLINICO POLICIAL PUCALLPA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AVENIDA AV. SAENZ PEAA NÂ° 421 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>Jr.SUCRE CUARTA CUADRA S/N  MZ B LOTE 18 Y 19- PUCALLPA S/N Jr.SUCRE CUARTA CUADRA S/N  MZ B LOTE 18 Y 19- PUCALLPA CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,27 +766,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.38068684</t>
+          <t>-8.39841364</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.53364066</t>
+          <t>-74.58801438</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CLINICA LAS AMERICAS</t>
+          <t>NUEVO BOLOGNESI.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JR. PROGRESO NÂ° 353 JR. PROGRESO NÂ° 353 CALLERIA CORONEL PORTILLO UCAYALI</t>
+          <t>JIRON JAUJA MZ K  LT 1 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.38308728</t>
+          <t>-8.37309373</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.53713647</t>
+          <t>-74.55099565</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO FABIANA DE LOS ANGELES E.I.R.L</t>
+          <t>NUEVO PARAISO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>07 de Junio NUMERO 254 MANZANA 70 LOTE 11 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>JIRON GRAU Nº 220 AA.HH. NUEVO PARAISO JIRON GRAU Nº 220 AA.HH. NUEVO PARAISO CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.37787604</t>
+          <t>-8.43305529</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.53498811</t>
+          <t>-74.24034814</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLOGICO AMERICANO - PUCALLPA</t>
+          <t>MAZARAY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JR. ATAHUALPA Nº 139 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO MAZARAY S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.37978211</t>
+          <t>-8.39836581</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.53559526</t>
+          <t>-74.29653113</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CLINICA DENTAL ORTIZ E.I.R.L</t>
+          <t>NUEVA BETANIA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JR. ZAVALA NÂ° 385  - MZ. 73 - LOTE 28 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CC.NN. NUEVA BETANIA S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.382345</t>
+          <t>-8.46232574</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.5376071</t>
+          <t>-74.16185514</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SANTA MARIA</t>
+          <t>ABUJAO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ZAVALA 580 2 AL COSTADO DE MI BANCO - SEGUNDO PISO CALLERIA CORONEL PORTILLO UCAYALI</t>
+          <t>OTROS CASERIO ABUJAO S/N NUMERO S/N DISTRITO MASISEA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.38594682</t>
+          <t>-8.4038413</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.52968456</t>
+          <t>-74.60283059</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN NORBERTO</t>
+          <t>NUEVA MAGDALENA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jr.CORONEL PORTILLO 518 - B DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>JIRON JUNIN S/N MZ 9 AA.HH. NUEVA MAGDALENA S/N JIRON JUNIN S/N MZ 9 AA.HH. NUEVA MAGDALENA CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.39377383</t>
+          <t>-8.08906357</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.57807864</t>
+          <t>-74.4263238</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO UNIVERSITARIO MAYUSHIN</t>
+          <t>SAN MIGUEL DE CALLERIA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CARRETERA FEDERICO BASADRE KM 6 200 INTERIOR UNIVERSIDAD NACIONAL DE UCAYALI DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>CALLE CASERIO SAN MIGUEL DE CALLERIA -MARGEN IZQUIERDA DEL RIO CALLERIA DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.3792869</t>
+          <t>-8.32331236</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-74.5448635</t>
+          <t>-74.50120992</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO NUEVO PARAISO</t>
+          <t>YANAMAYO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JOSE BALTA NUMERO 201 PISO 1 MANZANA F LOTE 06 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO YANAMAYO S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.3833115</t>
+          <t>-8.04804576</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.5324882</t>
+          <t>-74.65208643</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "NUEVO AMANECER"</t>
+          <t>TACSHITEA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AVENIDA SAN FERNANDO MANZANA 14 LOTE 7 DISTRITO MANANTAY PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>MALECON JION MALECON UCAYALI  CASERIO TACSHITEA S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,27 +1324,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.38565411</t>
+          <t>-8.259025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.54545493</t>
+          <t>-74.51063667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO BIOMEDIC</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PEDRO PAIVA 210 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO CHANCAY S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.37864466</t>
+          <t>-8.39181964</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.5298781</t>
+          <t>-74.5428795</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CLINICA DENTAL ASENCIOS  S.A.C</t>
+          <t>9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JR. ADOLFO MOREY 227 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>28 DE JULIO 486 AA.HH. 9 DE OCTUBRE CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,22 +1448,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.37930939</t>
+          <t>-8.37799548</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.53388296</t>
+          <t>-74.55485637</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CLINICA LAS AMERICAS II</t>
+          <t>CLAS TUPAC AMARU</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PROGRESO NUMERO 367 MANZANA 75 LOTE 13B DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS AA.HH. TUPAC AMARU MZ. I - LOTE 12 AA.HH. TUPAC AMARU MZ. I - LOTE 12 CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,27 +1510,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.39101862</t>
+          <t>-8.39059407</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-74.54506736</t>
+          <t>-74.40989687</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO MUNICIPAL DE ATENCION BASICA</t>
+          <t>SANTO DOMINGO DE MASHANGAY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OTROS AAHH 9 OCTUBRE LT 2 MZ 24 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO SANTO DOMINGO DE MASHANGAY S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.3905682</t>
+          <t>-8.3684339</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-74.5463562</t>
+          <t>-74.54870778</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>POLICLINICO 2 DE MAYO</t>
+          <t>JOSE OLAYA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AVENIDA 2 de mayo 757 A 100 metros de EsSalud Ucayali CALLERIA CORONEL PORTILLO UCAYALI</t>
+          <t>JIRON BOLOGNESI S/N MZ 1  LT 2 ASENTAMIENTO HUMANO JOSE OLAYA S/N JIRON BOLOGNESI S/N MZ 1  LT 2 ASENTAMIENTO HUMANO JOSE OLAYA CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,27 +1634,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.37708988</t>
+          <t>-8.41410641</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-74.53110414</t>
+          <t>-74.58724611</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PREVENVAC</t>
+          <t>LA FLORIDA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>JR. AGUSTAN CAUPER Nº 260 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO LA FLORIDA S/N CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250105</t>
+          <t>250101</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,37 +1691,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YARINACOCHA</t>
+          <t>CALLERIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.3646395</t>
+          <t>-8.292655</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-74.5665971</t>
+          <t>-74.44432333</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>POLICLINICO POLICIAL PUCALLPA</t>
+          <t>SANTA ELENA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jr.SUCRE CUARTA CUADRA S/N  MZ B LOTE 18 Y 19- PUCALLPA S/N Jr.SUCRE CUARTA CUADRA S/N  MZ B LOTE 18 Y 19- PUCALLPA CALLERIA CORONEL PORTILLO UCAYALI</t>
+          <t>OTROS CASERIO SANTA ELENA S/N S/N CASERIO SANTA ELENA S/N CALLERIA CORONEL PORTILLO UCAYALI</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,35 +1758,903 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.38434543</t>
+          <t>-8.0011356</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-74.53596867</t>
+          <t>-74.63100382</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CLINICA MATERNA SAN JUAN BOSCO</t>
+          <t>NUEVO SAPOSOA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONTAMANA NUMERO 128 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+          <t>OTROS CASERIO NUEVO SAPOSOA S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-8.38968347</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-74.54980684</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AVENIDA 3 DE ABRIL NUMERO 595 DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-8.39250131</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-74.53685151</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>REVOLUCION 432 AA.HH. BELLAVISTA CALLERIA CORONEL PORTILLO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-8.40618844</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-73.95270074</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ABUJAO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO SANTA ROSA DE ABUJAO S/N S/N CASERIO SANTA ROSA DE ABUJAO S/N MASISEA CORONEL PORTILLO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>I-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5455</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-8.40213197</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-74.41249531</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>EXITO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO EXITO S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-8.16565513</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-74.27318379</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SANTA SOFIA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO SANTA SOFIA -RIO UTUQUINIA CASERIO SANTA SOFIA -RIO UTUQUINIA CALLERIA CORONEL PORTILLO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-8.07269771</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-74.55642615</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CALLE COMUNIDAD NATIVA CALLERIA S/N RIO CALLERIA NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7417</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-8.38003769</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-74.38239467</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SANTA TERESA DE SHINUYA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO DE SANTA TERESA SHINUYA DISTRITO MANANTAY PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-8.01053075</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-74.585125</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PATRIA NUEVA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CALLE BAJO UCAYALI- RIO CALLERIA DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7224</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-8.44155166</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-74.3411176</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NUEVA ALIANZA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO NUEVA ALIANZA S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5462</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-8.16629486</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-74.61212445</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO SAN ANTONIO S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-8.4357704</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-74.25994117</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PUERTO BETHEL</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>OTROS CC.NN. PUERTO BETHEL S/N S/N CC.NN. PUERTO BETHEL S/N CALLERIA CORONEL PORTILLO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-8.36845371</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-74.53973251</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>JIRON ARENAL Nº 900 BARRIO EL ARENAL DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-8.39858296</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-74.36116898</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SANTA CARMELA DE MASHANGAY</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO SANTA CARMELA QUEBRADA  DE MASHANGAY DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-8.20779891</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-74.33778696</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NUEVO UTUQUINIA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>OTROS CASERIO NUEVO UTUQUINIA S/N NUMERO S/N DISTRITO CALLERIA PROVINCIA CORONEL PORTILLO DEPARTAMENTO UCAYALI</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>250101</t>
         </is>

--- a/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>30785</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.39377383</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>29247</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.3833115</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>21417</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.39101862</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>10148</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.3646395</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>5562</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.39841364</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>5565</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.37309373</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>5453</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.43305529</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>5460</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.39836581</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>5476</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.46232574</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>5560</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.4038413</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>5468</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.08906357</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>5575</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.32331236</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>5461</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-8.04804576</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>5574</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-8.259025</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>5556</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-8.39181964</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>5569</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-8.37799548</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>5456</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-8.39059407</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>5567</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-8.3684339</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>5561</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-8.41410641</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>5571</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-8.292655</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>5466</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-8.0011356</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>5558</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-8.38968347</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>5552</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-8.39250131</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>5480</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-8.40618844</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>5455</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-8.40213197</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>5463</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-8.16565513</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>5464</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-8.07269771</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>7417</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-8.38003769</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>10038</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-8.01053075</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>7224</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-8.44155166</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>5462</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-8.16629486</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>5452</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-8.4357704</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>5568</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-8.36845371</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>5457</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-8.39858296</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CALLERIA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>5465</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>250101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CALLERIA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-8.20779891</t>
@@ -2652,11 +2477,6 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>250101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/EstablecimientoSalud/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
